--- a/data/trans_bre/P1426-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P1426-Estudios-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,75</t>
+          <t>1,5</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>13,9%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 1,81</t>
+          <t>-1,25; 1,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 1,95</t>
+          <t>-1,63; 2,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 3,47</t>
+          <t>-1,38; 3,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-34,32; 85,8</t>
+          <t>-31,69; 88,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-33,32; 81,21</t>
+          <t>-36,72; 87,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-18,12; 35,37</t>
+          <t>-11,31; 41,78</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-0,87</t>
+          <t>-0,97</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-28,19%</t>
+          <t>-28,38%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,66</t>
+          <t>-0,6; 0,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 1,1</t>
+          <t>-0,29; 1,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 0,35</t>
+          <t>-1,87; -0,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-55,19; 101,08</t>
+          <t>-54,54; 99,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-24,14; 160,55</t>
+          <t>-22,8; 153,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-50,98; 12,8</t>
+          <t>-47,04; -2,55</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-1,01</t>
+          <t>-0,8</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-28,41%</t>
+          <t>-22,71%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 1,89</t>
+          <t>-1,55; 1,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 2,23</t>
+          <t>-0,75; 2,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 0,47</t>
+          <t>-2,33; 0,72</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-75,16; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-65,99; 763,02</t>
+          <t>-64,77; 633,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-57,82; 21,23</t>
+          <t>-51,16; 27,62</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-0,07</t>
+          <t>0,02</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-1,68%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 0,95</t>
+          <t>-0,34; 0,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 1,14</t>
+          <t>-0,07; 1,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 1,02</t>
+          <t>-0,81; 0,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-18,21; 80,5</t>
+          <t>-18,24; 75,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 100,15</t>
+          <t>-5,65; 102,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-23,71; 26,2</t>
+          <t>-15,86; 19,81</t>
         </is>
       </c>
     </row>
